--- a/models/sovereigns/United_Arab_Emirates_Sovereign_Model.xlsx
+++ b/models/sovereigns/United_Arab_Emirates_Sovereign_Model.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IMF CPI database via repo data record</t>
+          <t>IMF CPI database</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>general government debt</t>
+          <t>general government gross debt</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>World Bank WDI via repo data record</t>
+          <t>World Bank WDI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMF International Liquidity via repo data record</t>
+          <t>IMF International Liquidity</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross incl. gold (gold USD 9.7bn; ex gold USD 250.0bn)</t>
+          <t>gross incl. gold (ex gold USD 250.0bn; gold USD 9.7bn)</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>World Bank WDI via repo data record</t>
+          <t>World Bank WDI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">

--- a/models/sovereigns/United_Arab_Emirates_Sovereign_Model.xlsx
+++ b/models/sovereigns/United_Arab_Emirates_Sovereign_Model.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>general government gross debt</t>
+          <t>general government debt</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record</t>
+          <t>IMF WEO via repo data record (vintage unverified)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record</t>
+          <t>IMF WEO via repo data record (vintage unverified)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross incl. gold (ex gold USD 250.0bn; gold USD 9.7bn)</t>
+          <t>gross incl. gold (ex gold USD 250.0bn)</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>06-May-26</t>
+          <t>May-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/United_Arab_Emirates_Sovereign_Model.xlsx
+++ b/models/sovereigns/United_Arab_Emirates_Sovereign_Model.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IMF CPI database</t>
+          <t>IMF CPI database, via repo data record</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record</t>
+          <t>IMF WEO, via repo data record</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record</t>
+          <t>IMF WEO, via repo data record</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>general government debt</t>
+          <t>general government gross debt</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record (vintage unverified)</t>
+          <t>IMF WEO, via repo data record</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record (vintage unverified)</t>
+          <t>IMF WEO, via repo data record</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>World Bank WDI, via repo data record</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMF International Liquidity</t>
+          <t>IMF International Liquidity, via repo data record</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>World Bank WDI, via repo data record</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record</t>
+          <t>IMF WEO, via repo data record</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>May-26</t>
+          <t>06-May-26</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record, 09-Oct-26</t>
+          <t>IMF WEO via repo data record, 09-Oct-26 (vintage unverified)</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record, 09-Oct-26</t>
+          <t>IMF WEO via repo data record, 09-Oct-26 (vintage unverified)</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record, 09-Oct-26</t>
+          <t>IMF WEO via repo data record, 09-Oct-26 (vintage unverified)</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record, 09-Oct-26</t>
+          <t>IMF WEO via repo data record, 09-Oct-26 (vintage unverified)</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record, 09-Oct-26</t>
+          <t>IMF WEO via repo data record, 09-Oct-26 (vintage unverified)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/United_Arab_Emirates_Sovereign_Model.xlsx
+++ b/models/sovereigns/United_Arab_Emirates_Sovereign_Model.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IMF CPI database, via repo data record</t>
+          <t>IMF CPI database via repo data record</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF WEO, via repo data record</t>
+          <t>IMF WEO via repo data record</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF WEO, via repo data record</t>
+          <t>IMF WEO via repo data record</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>general government gross debt</t>
+          <t>general government debt</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF WEO, via repo data record</t>
+          <t>IMF WEO via repo data record</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IMF WEO, via repo data record</t>
+          <t>IMF WEO via repo data record</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>World Bank WDI, via repo data record</t>
+          <t>World Bank WDI via repo data record</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMF International Liquidity, via repo data record</t>
+          <t>IMF International Liquidity via repo data record</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>World Bank WDI, via repo data record</t>
+          <t>World Bank WDI via repo data record</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IMF WEO, via repo data record</t>
+          <t>IMF WEO via repo data record</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>06-May-26</t>
+          <t>May-26</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record, 09-Oct-26 (vintage unverified)</t>
+          <t>IMF WEO via repo data record, 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record, 09-Oct-26 (vintage unverified)</t>
+          <t>IMF WEO via repo data record, 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record, 09-Oct-26 (vintage unverified)</t>
+          <t>IMF WEO via repo data record, 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record, 09-Oct-26 (vintage unverified)</t>
+          <t>IMF WEO via repo data record, 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record, 09-Oct-26 (vintage unverified)</t>
+          <t>IMF WEO via repo data record, 09-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/United_Arab_Emirates_Sovereign_Model.xlsx
+++ b/models/sovereigns/United_Arab_Emirates_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/uae.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/uae.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/United_Arab_Emirates_Sovereign_Model.xlsx
+++ b/models/sovereigns/United_Arab_Emirates_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/uae.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/uae.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/United_Arab_Emirates_Sovereign_Model.xlsx
+++ b/models/sovereigns/United_Arab_Emirates_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/uae.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/uae.json</t>
         </is>
       </c>
     </row>
